--- a/Netflix Movies Analysis.xlsx
+++ b/Netflix Movies Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giris\OneDrive\Desktop\Data Ananlytics\Projects\Excel\Netflix Movies Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4343C9-5CF6-4BE7-8DB0-B04FAE314645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F008B94-8C4D-4B5A-8239-7457F98C9AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7D64DC3F-7C38-4A1E-BE57-DE5E142F4324}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D64DC3F-7C38-4A1E-BE57-DE5E142F4324}"/>
   </bookViews>
   <sheets>
     <sheet name="Back End" sheetId="4" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="107">
   <si>
     <t>Name</t>
   </si>
@@ -781,13 +781,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -801,1155 +801,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="202">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="114">
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -2935,9 +1787,6 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -2951,9 +1800,6 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -2967,25 +1813,6 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3019,6 +1846,13 @@
     </dxf>
     <dxf>
       <border>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -3103,6 +1937,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3116,6 +1953,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3129,6 +1969,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3357,13 +2200,6 @@
     </dxf>
     <dxf>
       <border>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -3448,9 +2284,6 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3464,9 +2297,6 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3480,9 +2310,6 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3548,6 +2375,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
@@ -3561,10 +2391,32 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3616,11 +2468,11 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Netflix Dark Red" pivot="0" table="0" count="10" xr9:uid="{56789B34-9C9F-4832-95B7-F07105EF4383}">
-      <tableStyleElement type="wholeTable" dxfId="201"/>
-      <tableStyleElement type="headerRow" dxfId="200"/>
+      <tableStyleElement type="wholeTable" dxfId="113"/>
+      <tableStyleElement type="headerRow" dxfId="112"/>
     </tableStyle>
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{191304D1-5282-4984-AC5A-501DF62AA1AD}">
-      <tableStyleElement type="wholeTable" dxfId="199"/>
+      <tableStyleElement type="wholeTable" dxfId="111"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -4004,61 +2856,79 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Back End'!$A$12:$A$30</c:f>
+              <c:f>'Back End'!$A$12:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1960</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>1972</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1991</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>1993</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>1994</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1999</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>2006</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="13">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="14">
                   <c:v>2008</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="17">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="18">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="19">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="20">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="21">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>2019</c:v>
                 </c:pt>
               </c:strCache>
@@ -4066,10 +2936,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Back End'!$B$12:$B$30</c:f>
+              <c:f>'Back End'!$B$12:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4077,51 +2947,69 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -4815,6 +3703,15 @@
             <c:idx val="0"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="E50914"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000005-ADDC-46C4-B2CF-C7790124F334}"/>
@@ -4844,15 +3741,6 @@
             <c:idx val="2"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="E50914"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-ADDC-46C4-B2CF-C7790124F334}"/>
@@ -4899,6 +3787,28 @@
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.15871398326590391"/>
+                  <c:y val="0"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-ADDC-46C4-B2CF-C7790124F334}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
@@ -4924,7 +3834,7 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.15871398326590391"/>
+                  <c:x val="0.17357346906222348"/>
                   <c:y val="0"/>
                 </c:manualLayout>
               </c:layout>
@@ -5044,13 +3954,13 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Fight Club </c:v>
+                  <c:v>Pulp Fiction </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Schindler's List </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Pulp Fiction </c:v>
+                  <c:v>The Dark Knight </c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>The Godfather </c:v>
@@ -5068,13 +3978,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.8000000000000007</c:v>
+                  <c:v>8.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.9</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9.1999999999999993</c:v>
@@ -6697,25 +5607,22 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Back End'!$A$64:$A$70</c:f>
+              <c:f>'Back End'!$A$64:$A$69</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v> Action/Drama </c:v>
+                  <c:v> Action/Crime </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v> Action/Sci-Fi </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> Biography/Drama </c:v>
+                  <c:v> Crime/Drama </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> Crime/Drama </c:v>
+                  <c:v> Drama/Music </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> Drama/Music </c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v> Horror/Thriller </c:v>
                 </c:pt>
               </c:strCache>
@@ -6723,10 +5630,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Back End'!$B$64:$B$70</c:f>
+              <c:f>'Back End'!$B$64:$B$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -6734,15 +5641,12 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>9</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -6855,25 +5759,22 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Back End'!$A$64:$A$70</c:f>
+              <c:f>'Back End'!$A$64:$A$69</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v> Action/Drama </c:v>
+                  <c:v> Action/Crime </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v> Action/Sci-Fi </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> Biography/Drama </c:v>
+                  <c:v> Crime/Drama </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> Crime/Drama </c:v>
+                  <c:v> Drama/Music </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> Drama/Music </c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v> Horror/Thriller </c:v>
                 </c:pt>
               </c:strCache>
@@ -6881,26 +5782,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Back End'!$C$64:$C$70</c:f>
+              <c:f>'Back End'!$C$64:$C$69</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.9</c:v>
+                  <c:v>8.5111111111111128</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.5111111111111111</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -7319,13 +6217,13 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Fight Club </c:v>
+                  <c:v>Pulp Fiction </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Schindler's List </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Pulp Fiction </c:v>
+                  <c:v>The Dark Knight </c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>The Godfather </c:v>
@@ -7343,13 +6241,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.8000000000000007</c:v>
+                  <c:v>8.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.9</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9.1999999999999993</c:v>
@@ -9616,61 +8514,79 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Back End'!$A$12:$A$30</c:f>
+              <c:f>'Back End'!$A$12:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>1960</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>1972</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1991</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>1993</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>1994</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1999</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>2006</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="13">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="14">
                   <c:v>2008</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="17">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="18">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="19">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="20">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="21">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>2019</c:v>
                 </c:pt>
               </c:strCache>
@@ -9678,10 +8594,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Back End'!$B$12:$B$30</c:f>
+              <c:f>'Back End'!$B$12:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9689,51 +8605,69 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="22">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -10316,25 +9250,22 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Back End'!$A$64:$A$70</c:f>
+              <c:f>'Back End'!$A$64:$A$69</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v> Action/Drama </c:v>
+                  <c:v> Action/Crime </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v> Action/Sci-Fi </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> Biography/Drama </c:v>
+                  <c:v> Crime/Drama </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> Crime/Drama </c:v>
+                  <c:v> Drama/Music </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> Drama/Music </c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v> Horror/Thriller </c:v>
                 </c:pt>
               </c:strCache>
@@ -10342,10 +9273,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Back End'!$B$64:$B$70</c:f>
+              <c:f>'Back End'!$B$64:$B$69</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -10353,15 +9284,12 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>9</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -10416,25 +9344,22 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Back End'!$A$64:$A$70</c:f>
+              <c:f>'Back End'!$A$64:$A$69</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v> Action/Drama </c:v>
+                  <c:v> Action/Crime </c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v> Action/Sci-Fi </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> Biography/Drama </c:v>
+                  <c:v> Crime/Drama </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> Crime/Drama </c:v>
+                  <c:v> Drama/Music </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> Drama/Music </c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v> Horror/Thriller </c:v>
                 </c:pt>
               </c:strCache>
@@ -10442,26 +9367,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Back End'!$C$64:$C$70</c:f>
+              <c:f>'Back End'!$C$64:$C$69</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.9</c:v>
+                  <c:v>8.5111111111111128</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.5111111111111111</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -16799,7 +15721,7 @@
                 <a:cs typeface="Calibri"/>
               </a:rPr>
               <a:pPr/>
-              <a:t>31</a:t>
+              <a:t>50</a:t>
             </a:fld>
             <a:endParaRPr lang="en-IN" sz="3600">
               <a:solidFill>
@@ -19623,984 +18545,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93214055-283B-4697-87ED-1D1043E1BA7E}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="63">
-  <location ref="A99:B116" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
-      <items count="22">
-        <item x="3"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="17"/>
-        <item x="7"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="2"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="16"/>
-        <item x="0"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="17">
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Category" fld="4" subtotal="count" baseField="4" baseItem="2"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="149">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="148">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="147">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="146">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="145">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="144">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E870BC7B-18CC-42DD-A155-CC625DED6671}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A181:B183" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="198">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="197">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="196">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="195">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="194">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="193">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A930A240-A9A6-4779-AE87-FE50293892FB}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A189:A190" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Duration" fld="3" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="153">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="152">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="151">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="150">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F78E4D2B-4055-47EF-8D38-598B5EE8EB34}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="31">
-  <location ref="A40:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="158">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="157">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="156">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="155">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="154">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="17" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="13">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DE8ADC1-232D-449D-9F3B-089A9B7F9256}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="60">
-  <location ref="A63:C70" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="22">
-        <item x="3"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="17"/>
-        <item x="7"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="2"/>
-        <item x="14"/>
-        <item x="18"/>
-        <item x="16"/>
-        <item x="0"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Average of IMDb Rating" fld="5" subtotal="average" baseField="4" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="164">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="163">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="162">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="161">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="5">
-            <x v="1"/>
-            <x v="3"/>
-            <x v="10"/>
-            <x v="12"/>
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="160">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="159">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="41" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="41" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="47" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="47" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="4" type="count" evalOrder="-1" id="2" iMeasureFld="1">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DE7D564-62D5-4F5C-B8A8-50A2F7E7A2CA}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="A11:B30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="25">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="21"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="170">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="169">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="168">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="167">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="166">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="165">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="7" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD170DB0-92A0-439A-86DF-3939E2F8CB4A}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="40">
-  <location ref="A51:B55" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="176">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="175">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="174">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="173">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="172">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="171">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="32" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="32" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="32" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="32" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="34" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{193165D1-1C42-4172-BD12-8E1ED9DB29BE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="66">
   <location ref="A81:B87" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -20671,8 +18615,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -20687,13 +18631,13 @@
   </rowFields>
   <rowItems count="6">
     <i>
-      <x v="41"/>
+      <x v="25"/>
     </i>
     <i>
       <x v="23"/>
     </i>
     <i>
-      <x v="25"/>
+      <x v="16"/>
     </i>
     <i>
       <x v="14"/>
@@ -20712,16 +18656,16 @@
     <dataField name="Sum of IMDb Rating" fld="5" baseField="0" baseItem="5"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="182">
+    <format dxfId="61">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="181">
+    <format dxfId="60">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="180">
+    <format dxfId="59">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="179">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="5">
@@ -20734,10 +18678,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="178">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="177">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -20851,9 +18795,233 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A930A240-A9A6-4779-AE87-FE50293892FB}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A189:A190" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Duration" fld="3" subtotal="average" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="110">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="109">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="108">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="107">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F78E4D2B-4055-47EF-8D38-598B5EE8EB34}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="31">
+  <location ref="A40:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="66">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="64">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="17" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{415DA769-B38C-4D4E-8E03-95C7115EDE4F}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A126:B158" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A126:B177" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="51">
@@ -20922,8 +19090,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -20936,12 +19104,15 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="32">
+  <rowItems count="51">
     <i>
       <x v="44"/>
     </i>
     <i>
       <x v="35"/>
+    </i>
+    <i>
+      <x v="33"/>
     </i>
     <i>
       <x v="26"/>
@@ -20950,40 +19121,64 @@
       <x v="24"/>
     </i>
     <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
       <x v="8"/>
+    </i>
+    <i>
+      <x v="15"/>
     </i>
     <i>
       <x v="40"/>
     </i>
     <i>
-      <x v="45"/>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="37"/>
     </i>
     <i>
       <x v="22"/>
     </i>
     <i>
-      <x v="37"/>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="31"/>
     </i>
     <i>
       <x v="23"/>
     </i>
     <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="12"/>
+      <x v="4"/>
     </i>
     <i>
       <x v="49"/>
     </i>
     <i>
-      <x v="17"/>
+      <x v="34"/>
     </i>
     <i>
       <x v="5"/>
+    </i>
+    <i>
+      <x v="17"/>
     </i>
     <i>
       <x/>
@@ -20992,40 +19187,70 @@
       <x v="47"/>
     </i>
     <i>
+      <x v="36"/>
+    </i>
+    <i>
       <x v="29"/>
+    </i>
+    <i>
+      <x v="13"/>
     </i>
     <i>
       <x v="20"/>
     </i>
     <i>
-      <x v="13"/>
+      <x v="42"/>
     </i>
     <i>
-      <x v="36"/>
+      <x v="32"/>
     </i>
     <i>
       <x v="14"/>
     </i>
     <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
       <x v="27"/>
     </i>
     <i>
-      <x v="42"/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
     </i>
     <i>
       <x v="2"/>
     </i>
     <i>
-      <x v="11"/>
+      <x v="46"/>
     </i>
     <i>
       <x v="25"/>
+    </i>
+    <i>
+      <x v="11"/>
     </i>
     <i>
       <x v="21"/>
     </i>
     <i>
       <x v="19"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i>
       <x v="43"/>
@@ -21041,29 +19266,29 @@
     <dataField name="Max of IMDb Rating" fld="5" subtotal="max" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="189">
+    <format dxfId="73">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="188">
+    <format dxfId="72">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="187">
+    <format dxfId="71">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="186">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="185">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="184">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="183">
+    <format dxfId="67">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -21079,7 +19304,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4D4DA109-D2E1-46BB-8A85-17E83AAAE7E1}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B4" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="7">
@@ -21087,8 +19312,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -21117,13 +19342,13 @@
     <dataField name="Average of IMDb Rating" fld="5" subtotal="average" baseField="0" baseItem="1"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="192">
+    <format dxfId="76">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="191">
+    <format dxfId="75">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="190">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -21132,6 +19357,796 @@
           </reference>
         </references>
       </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DE8ADC1-232D-449D-9F3B-089A9B7F9256}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="60">
+  <location ref="A63:C69" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="22">
+        <item x="3"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="17"/>
+        <item x="7"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of IMDb Rating" fld="5" subtotal="average" baseField="4" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="82">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="81">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="80">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="79">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="5">
+            <x v="1"/>
+            <x v="3"/>
+            <x v="10"/>
+            <x v="12"/>
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="78">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="77">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="41" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="41" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="47" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="47" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="4" type="count" evalOrder="-1" id="2" iMeasureFld="1">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E870BC7B-18CC-42DD-A155-CC625DED6671}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A181:B185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="88">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="87">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="86">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="85">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="84">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="83">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DE7D564-62D5-4F5C-B8A8-50A2F7E7A2CA}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="A11:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="25">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="21"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="25">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="94">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="93">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="92">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="91">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="90">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="89">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="7" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD170DB0-92A0-439A-86DF-3939E2F8CB4A}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="40">
+  <location ref="A51:B55" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="100">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="99">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="98">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="97">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="96">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="95">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="32" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93214055-283B-4697-87ED-1D1043E1BA7E}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="63">
+  <location ref="A99:B121" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="22">
+        <item x="3"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="17"/>
+        <item x="7"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="22">
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Category" fld="4" subtotal="count" baseField="4" baseItem="2"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="106">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="105">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="104">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="103">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="102">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="101">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -21161,8 +20176,8 @@
   <data>
     <tabular pivotCacheId="1488919595">
       <items count="3">
-        <i x="0"/>
-        <i x="2"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
         <i x="1" s="1"/>
       </items>
     </tabular>
@@ -21177,16 +20192,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70D207F-E393-4FED-81F1-F57A389A22FD}" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0" headerRowDxfId="143" dataDxfId="141" headerRowBorderDxfId="142" tableBorderDxfId="140" totalsRowBorderDxfId="139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70D207F-E393-4FED-81F1-F57A389A22FD}" name="Table1" displayName="Table1" ref="A1:G51" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
   <autoFilter ref="A1:G51" xr:uid="{B70D207F-E393-4FED-81F1-F57A389A22FD}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D7D47CA0-5846-4CF0-8A3E-F554DDA9A6F6}" name="Name" dataDxfId="138"/>
-    <tableColumn id="2" xr3:uid="{A06F8592-77FA-4212-B416-D4C5A88973FE}" name="Year" dataDxfId="137"/>
-    <tableColumn id="3" xr3:uid="{F1F0C655-0310-4B28-9B39-8D32CB9379E6}" name="Age Rating" dataDxfId="136"/>
-    <tableColumn id="7" xr3:uid="{6ACF3390-F9E2-4CC1-B949-CE35AD884DA9}" name="Duration" dataDxfId="135"/>
-    <tableColumn id="5" xr3:uid="{723DC84C-8244-4258-B24E-72C880F593E0}" name="Category" dataDxfId="134"/>
-    <tableColumn id="6" xr3:uid="{C5511E04-8342-4C09-886B-9F8A8ED64A29}" name="IMDb Rating" dataDxfId="133"/>
-    <tableColumn id="4" xr3:uid="{AFC9F45A-4BB4-4567-AA46-8E6CAB7C827A}" name="Rating Range" dataDxfId="132">
+    <tableColumn id="1" xr3:uid="{D7D47CA0-5846-4CF0-8A3E-F554DDA9A6F6}" name="Name" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{A06F8592-77FA-4212-B416-D4C5A88973FE}" name="Year" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{F1F0C655-0310-4B28-9B39-8D32CB9379E6}" name="Age Rating" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{6ACF3390-F9E2-4CC1-B949-CE35AD884DA9}" name="Duration" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{723DC84C-8244-4258-B24E-72C880F593E0}" name="Category" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{C5511E04-8342-4C09-886B-9F8A8ED64A29}" name="IMDb Rating" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{AFC9F45A-4BB4-4567-AA46-8E6CAB7C827A}" name="Rating Range" dataDxfId="44">
       <calculatedColumnFormula>IF(Table1[[#This Row],[IMDb Rating]]&gt;=9,"9+",IF(Table1[[#This Row],[IMDb Rating]]&gt;=8,"8 - 8.9",IF(Table1[[#This Row],[IMDb Rating]]&gt;=7,"7-7.9","Below 7")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -21518,15 +20533,15 @@
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="46">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B4" s="47">
-        <v>8.2967741935483872</v>
+        <v>8.2620000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="42"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
@@ -21539,11 +20554,11 @@
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <f>GETPIVOTDATA("Count of Name",$A$3)</f>
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B7" s="15">
         <f>GETPIVOTDATA("Average of IMDb Rating",$A$3)</f>
-        <v>8.2967741935483872</v>
+        <v>8.2620000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -21563,7 +20578,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
-        <v>1960</v>
+        <v>1942</v>
       </c>
       <c r="B12" s="43">
         <v>1</v>
@@ -21571,7 +20586,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="26">
-        <v>1972</v>
+        <v>1960</v>
       </c>
       <c r="B13" s="43">
         <v>1</v>
@@ -21579,15 +20594,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="26">
-        <v>1991</v>
+        <v>1972</v>
       </c>
       <c r="B14" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="26">
-        <v>1993</v>
+        <v>1977</v>
       </c>
       <c r="B15" s="43">
         <v>1</v>
@@ -21595,23 +20610,23 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="26">
-        <v>1994</v>
+        <v>1982</v>
       </c>
       <c r="B16" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="26">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B17" s="43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="26">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="B18" s="43">
         <v>1</v>
@@ -21619,15 +20634,15 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
-        <v>2006</v>
+        <v>1994</v>
       </c>
       <c r="B19" s="43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="26">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="B20" s="43">
         <v>1</v>
@@ -21635,15 +20650,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="26">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="B21" s="43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="26">
-        <v>2012</v>
+        <v>2000</v>
       </c>
       <c r="B22" s="43">
         <v>1</v>
@@ -21651,70 +20666,116 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="26">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="B23" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="26">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B24" s="43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="26">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B25" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="26">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B26" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="26">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B27" s="43">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="26">
+        <v>2012</v>
+      </c>
+      <c r="B28" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="26">
+        <v>2013</v>
+      </c>
+      <c r="B29" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="26">
+        <v>2014</v>
+      </c>
+      <c r="B30" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="26">
+        <v>2015</v>
+      </c>
+      <c r="B31" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="26">
+        <v>2016</v>
+      </c>
+      <c r="B32" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="26">
+        <v>2017</v>
+      </c>
+      <c r="B33" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="26">
         <v>2018</v>
       </c>
-      <c r="B28" s="43">
-        <v>1</v>
+      <c r="B34" s="43">
+        <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="27">
+    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="27">
         <v>2019</v>
       </c>
-      <c r="B29" s="43">
+      <c r="B35" s="43">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="27" t="s">
+    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="44">
-        <v>31</v>
+      <c r="B36" s="44">
+        <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="38" t="s">
@@ -21814,7 +20875,7 @@
       <c r="A62" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="B62" s="42"/>
+      <c r="B62" s="40"/>
       <c r="C62" s="39"/>
     </row>
     <row r="63" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -21829,18 +20890,18 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="18" t="s">
-        <v>25</v>
+      <c r="A64" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="B64" s="48">
         <v>1</v>
       </c>
       <c r="C64" s="20">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="27" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="26" t="s">
         <v>19</v>
       </c>
       <c r="B65" s="48">
@@ -21851,30 +20912,30 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
-        <v>52</v>
+      <c r="A66" s="26" t="s">
+        <v>13</v>
       </c>
       <c r="B66" s="48">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C66" s="20">
-        <v>8.9</v>
+        <v>8.5111111111111128</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="26" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B67" s="48">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C67" s="20">
-        <v>8.5111111111111111</v>
+        <v>8.5</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="26" t="s">
-        <v>65</v>
+    <row r="68" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="27" t="s">
+        <v>11</v>
       </c>
       <c r="B68" s="48">
         <v>1</v>
@@ -21885,24 +20946,13 @@
     </row>
     <row r="69" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="48">
-        <v>1</v>
-      </c>
-      <c r="C69" s="20">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B70" s="45">
-        <v>15</v>
-      </c>
-      <c r="C70" s="21">
-        <v>8.5466666666666651</v>
+      <c r="B69" s="45">
+        <v>14</v>
+      </c>
+      <c r="C69" s="21">
+        <v>8.5571428571428552</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -21921,11 +20971,11 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="18" t="s">
-        <v>55</v>
+      <c r="A82" s="26" t="s">
+        <v>50</v>
       </c>
       <c r="B82" s="43">
-        <v>8.8000000000000007</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -21938,10 +20988,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="26" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B84" s="43">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -21965,7 +21015,7 @@
         <v>81</v>
       </c>
       <c r="B87" s="44">
-        <v>45.099999999999994</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -21993,10 +21043,10 @@
     </row>
     <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="26" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="B101" s="43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D101" s="16" t="s">
         <v>89</v>
@@ -22008,34 +21058,34 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="26" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B102" s="43">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="26" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B103" s="43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="26" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B104" s="43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="26" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="B105" s="43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -22043,44 +21093,44 @@
         <v>57</v>
       </c>
       <c r="B106" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="26" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B107" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="26" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B108" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B109" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="26" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B110" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="26" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B111" s="43">
         <v>1</v>
@@ -22088,7 +21138,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="26" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="B112" s="43">
         <v>1</v>
@@ -22096,7 +21146,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="26" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B113" s="43">
         <v>1</v>
@@ -22104,30 +21154,68 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="26" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B114" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="27" t="s">
-        <v>25</v>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="B115" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="27" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B116" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B117" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B118" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B120" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B116" s="44">
-        <v>31</v>
+      <c r="B121" s="44">
+        <v>50</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="38" t="s">
@@ -22168,15 +21256,15 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="26" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B129" s="43">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B130" s="43">
         <v>8.9</v>
@@ -22184,230 +21272,380 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="26" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B131" s="43">
-        <v>8.8000000000000007</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B132" s="43">
-        <v>8.6999999999999993</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B133" s="43">
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="26" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B134" s="43">
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="26" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B135" s="43">
-        <v>8.6</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="26" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B136" s="43">
-        <v>8.5</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="26" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B137" s="43">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="26" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B138" s="43">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="26" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B139" s="43">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="26" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B140" s="43">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B141" s="43">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B142" s="43">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="26" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="B143" s="43">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B144" s="43">
-        <v>8.1999999999999993</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="26" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B145" s="43">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="26" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="B146" s="43">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="26" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B147" s="43">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B148" s="43">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="26" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B149" s="43">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="26" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B150" s="43">
-        <v>8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="B151" s="43">
-        <v>8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="26" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B152" s="43">
-        <v>7.7</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="26" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B153" s="43">
-        <v>7.7</v>
+        <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="26" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B154" s="43">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B155" s="43">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B156" s="43">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B157" s="43">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B158" s="43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B159" s="43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B160" s="43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B161" s="43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B162" s="43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B163" s="43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B164" s="43">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B165" s="43">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B166" s="43">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B167" s="43">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B168" s="43">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B169" s="43">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B170" s="43">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B171" s="43">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B172" s="43">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B156" s="43">
+      <c r="B173" s="43">
         <v>7.4</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="27" t="s">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" s="43">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B175" s="43">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B157" s="43">
+      <c r="B176" s="43">
         <v>7.3</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="27" t="s">
+    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B158" s="49">
+      <c r="B177" s="49">
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="176" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="38" t="s">
@@ -22424,7 +21662,7 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="27" t="s">
+      <c r="A182" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B182" s="43">
@@ -22438,15 +21676,30 @@
         <v xml:space="preserve"> R </v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="27" t="s">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B183" s="43">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B183" s="44">
-        <v>31</v>
+      <c r="B185" s="44">
+        <v>50</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="25" t="s">
@@ -22460,7 +21713,7 @@
     </row>
     <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="37">
-        <v>135.90322580645162</v>
+        <v>135.66</v>
       </c>
       <c r="D190" s="24" t="s">
         <v>95</v>
@@ -22472,16 +21725,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="A180:B180"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId11"/>
